--- a/backend/tests/data/input_data.xlsx
+++ b/backend/tests/data/input_data.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F41"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -847,9 +847,389 @@
         <v>NV Tour</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>AB</v>
+      </c>
+      <c r="B23" t="str">
+        <v>0900000022</v>
+      </c>
+      <c r="C23" t="str">
+        <v>nv22@test.com</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F23" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>ABC</v>
+      </c>
+      <c r="B24" t="str">
+        <v>0900000023</v>
+      </c>
+      <c r="C24" t="str">
+        <v>nv23@test.com</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F24" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</v>
+      </c>
+      <c r="B25" t="str">
+        <v>0900000024</v>
+      </c>
+      <c r="C25" t="str">
+        <v>nv24@test.com</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F25" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>12345</v>
+      </c>
+      <c r="B26" t="str">
+        <v>0900000025</v>
+      </c>
+      <c r="C26" t="str">
+        <v>nv25@test.com</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F26" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B27" t="str">
+        <v>09000000</v>
+      </c>
+      <c r="C27" t="str">
+        <v>nv26@test.com</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F27" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B28" t="str">
+        <v>09000000001</v>
+      </c>
+      <c r="C28" t="str">
+        <v>nv27@test.com</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F28" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B29" t="str">
+        <v>1900000028</v>
+      </c>
+      <c r="C29" t="str">
+        <v>nv28@test.com</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F29" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B30" t="str">
+        <v>0900-000029</v>
+      </c>
+      <c r="C30" t="str">
+        <v>nv29@test.com</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F30" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B31" t="str">
+        <v>0900000030</v>
+      </c>
+      <c r="C31" t="str">
+        <v>user@domain</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F31" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B32" t="str">
+        <v>0900000031</v>
+      </c>
+      <c r="C32" t="str">
+        <v>user@.com</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F32" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B33" t="str">
+        <v>0900000032</v>
+      </c>
+      <c r="C33" t="str">
+        <v>user@@domain.com</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F33" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B34" t="str">
+        <v>0900000034</v>
+      </c>
+      <c r="C34" t="str">
+        <v>nv34@test.com</v>
+      </c>
+      <c r="D34" t="str">
+        <v>a</v>
+      </c>
+      <c r="E34" t="str">
+        <v>a</v>
+      </c>
+      <c r="F34" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B35" t="str">
+        <v>0900000035</v>
+      </c>
+      <c r="C35" t="str">
+        <v>nv35@test.com</v>
+      </c>
+      <c r="D35" t="str">
+        <v>abcde</v>
+      </c>
+      <c r="E35" t="str">
+        <v>abcde</v>
+      </c>
+      <c r="F35" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B36" t="str">
+        <v>0900000036</v>
+      </c>
+      <c r="C36" t="str">
+        <v>nv36@test.com</v>
+      </c>
+      <c r="D36" t="str">
+        <v>abcdef</v>
+      </c>
+      <c r="E36" t="str">
+        <v>abcdef</v>
+      </c>
+      <c r="F36" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B37" t="str">
+        <v>0900000037</v>
+      </c>
+      <c r="C37" t="str">
+        <v>nv37@test.com</v>
+      </c>
+      <c r="D37" t="str">
+        <v>abcdefg</v>
+      </c>
+      <c r="E37" t="str">
+        <v>abcdefg</v>
+      </c>
+      <c r="F37" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B38" t="str">
+        <v>0900000038</v>
+      </c>
+      <c r="C38" t="str">
+        <v>nv38@test.com</v>
+      </c>
+      <c r="D38" t="str">
+        <v>123456</v>
+      </c>
+      <c r="E38" t="str">
+        <v>123456</v>
+      </c>
+      <c r="F38" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B39" t="str">
+        <v>0900000039</v>
+      </c>
+      <c r="C39" t="str">
+        <v>nv39@test.com</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Nguyễn Văn A</v>
+      </c>
+      <c r="B40" t="str">
+        <v>0900000040</v>
+      </c>
+      <c r="C40" t="str">
+        <v>admin@gmail.com</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F40" t="str">
+        <v>NV Booking</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v xml:space="preserve">  Nguyễn Văn A  </v>
+      </c>
+      <c r="B41" t="str">
+        <v>0900000041</v>
+      </c>
+      <c r="C41" t="str">
+        <v>nv41@test.com</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Matkhau@123</v>
+      </c>
+      <c r="F41" t="str">
+        <v>NV Tour</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F41"/>
   </ignoredErrors>
 </worksheet>
 </file>